--- a/outputs/evaluation/decision/v2/CF_M08/run_3/CF_M08_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M08/run_3/CF_M08_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,22 +471,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M08_AD03</t>
+          <t>CF_M08_AD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
+directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>*CF_M08_C11, *CF_M08_C12</t>
+          <t>*CF_M08_C10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CF_M08_AU22</t>
+          <t>CF_M08_AU03</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -494,90 +495,90 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Security; Integrity</t>
+          <t>Responsiveness</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Traefik</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Traefik opens port 443 to handle HTTPS traffic, which is the standard for secure communications on the web. HTTPS encrypts the data transmitted between clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>Traefik acts as a reverse proxy and load balancer, distributing traffic between multiple instances of a service, improving the availability and responsiveness of the application.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.8749</v>
+        <v>0.7348</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M08_AD04</t>
+          <t>CF_M08_AD03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
+          <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>*CF_M08_C14</t>
+          <t>*CF_M08_C11, *CF_M08_C12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CF_M08_AU05</t>
+          <t>CF_M08_AU22</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ease</t>
+          <t>Security; Integrity</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Next.js</t>
+          <t>Docker</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>Traefik acts as a reverse proxy and load balancer, distributing traffic between multiple instances of a service, improving the availability and responsiveness of the application.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.584</v>
+        <v>0.6052</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M08_AD05</t>
+          <t>CF_M08_AD04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
+          <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*CF_M08_C15</t>
+          <t>*CF_M08_C14</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -590,7 +591,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stylization</t>
+          <t>Ease</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -609,7 +610,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="5">
@@ -648,16 +649,16 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Traefik acts as a reverse proxy and load balancer, distributing traffic between multiple instances of a service, improving the availability and responsiveness of the application.</t>
+          <t>Next.js supports both client-side rendering (CSR) and server-side rendering (SSR), allowing to choose the best strategy according to the needs of the application.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.6473</v>
+        <v>0.6556</v>
       </c>
     </row>
     <row r="6">
@@ -734,7 +735,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Efficiency (of development); Flexibility</t>
+          <t>Efficiency; Flexibility</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -840,16 +841,16 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>Prisma is an ORM tool used to simplify database access and management.</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.653</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="10">
@@ -888,64 +889,16 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_07</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
+          <t>Prisma is an ORM tool used to simplify database access and management.</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.5518999999999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M08_AD12</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>*CF_M08_C24</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CF_M08_AU09</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Depuration</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Prisma</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>AD_04</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7723</v>
       </c>
     </row>
   </sheetData>
